--- a/Comparison Analysis/Results/Output_monthly_mean_visits-Unadjusted.xlsx
+++ b/Comparison Analysis/Results/Output_monthly_mean_visits-Unadjusted.xlsx
@@ -387,16 +387,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2.601834061135371</v>
+        <v>9.357379912663756</v>
       </c>
       <c r="C2">
-        <v>2.602</v>
+        <v>9.356999999999999</v>
       </c>
       <c r="D2">
-        <v>2.567</v>
+        <v>9.196</v>
       </c>
       <c r="E2">
-        <v>2.637</v>
+        <v>9.519</v>
       </c>
     </row>
     <row r="3">
@@ -404,16 +404,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1.810131004366812</v>
+        <v>6.575545851528385</v>
       </c>
       <c r="C3">
-        <v>1.81</v>
+        <v>6.576</v>
       </c>
       <c r="D3">
-        <v>1.78</v>
+        <v>6.435</v>
       </c>
       <c r="E3">
-        <v>1.841</v>
+        <v>6.718</v>
       </c>
     </row>
     <row r="4">
@@ -421,16 +421,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1.645982532751092</v>
+        <v>6.238864628820961</v>
       </c>
       <c r="C4">
-        <v>1.646</v>
+        <v>6.239</v>
       </c>
       <c r="D4">
-        <v>1.616</v>
+        <v>6.092</v>
       </c>
       <c r="E4">
-        <v>1.675</v>
+        <v>6.386</v>
       </c>
     </row>
     <row r="5">
@@ -438,16 +438,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1.366506550218341</v>
+        <v>5.23235807860262</v>
       </c>
       <c r="C5">
-        <v>1.367</v>
+        <v>5.232</v>
       </c>
       <c r="D5">
-        <v>1.339</v>
+        <v>5.099</v>
       </c>
       <c r="E5">
-        <v>1.394</v>
+        <v>5.364</v>
       </c>
     </row>
     <row r="6">
@@ -455,16 +455,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1.249170305676856</v>
+        <v>4.85532751091703</v>
       </c>
       <c r="C6">
-        <v>1.249</v>
+        <v>4.855</v>
       </c>
       <c r="D6">
-        <v>1.222</v>
+        <v>4.71</v>
       </c>
       <c r="E6">
-        <v>1.276</v>
+        <v>5.004</v>
       </c>
     </row>
     <row r="7">
@@ -472,16 +472,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>1.114978165938865</v>
+        <v>4.268078602620087</v>
       </c>
       <c r="C7">
-        <v>1.115</v>
+        <v>4.268</v>
       </c>
       <c r="D7">
-        <v>1.091</v>
+        <v>4.145</v>
       </c>
       <c r="E7">
-        <v>1.14</v>
+        <v>4.397</v>
       </c>
     </row>
     <row r="8">
@@ -489,16 +489,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1.065764192139738</v>
+        <v>4.113187772925764</v>
       </c>
       <c r="C8">
-        <v>1.066</v>
+        <v>4.113</v>
       </c>
       <c r="D8">
-        <v>1.041</v>
+        <v>3.99</v>
       </c>
       <c r="E8">
-        <v>1.09</v>
+        <v>4.232</v>
       </c>
     </row>
     <row r="9">
@@ -506,16 +506,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.9679039301310044</v>
+        <v>3.844235807860262</v>
       </c>
       <c r="C9">
-        <v>0.968</v>
+        <v>3.844</v>
       </c>
       <c r="D9">
-        <v>0.945</v>
+        <v>3.723</v>
       </c>
       <c r="E9">
-        <v>0.99</v>
+        <v>3.966</v>
       </c>
     </row>
     <row r="10">
@@ -523,16 +523,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.9512663755458516</v>
+        <v>3.739825327510917</v>
       </c>
       <c r="C10">
-        <v>0.951</v>
+        <v>3.74</v>
       </c>
       <c r="D10">
-        <v>0.928</v>
+        <v>3.616</v>
       </c>
       <c r="E10">
-        <v>0.975</v>
+        <v>3.864</v>
       </c>
     </row>
     <row r="11">
@@ -540,16 +540,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.9095196506550218</v>
+        <v>3.598864628820961</v>
       </c>
       <c r="C11">
-        <v>0.91</v>
+        <v>3.599</v>
       </c>
       <c r="D11">
-        <v>0.886</v>
+        <v>3.472</v>
       </c>
       <c r="E11">
-        <v>0.9330000000000001</v>
+        <v>3.726</v>
       </c>
     </row>
     <row r="12">
@@ -557,16 +557,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.8556331877729257</v>
+        <v>3.418427947598253</v>
       </c>
       <c r="C12">
-        <v>0.856</v>
+        <v>3.418</v>
       </c>
       <c r="D12">
-        <v>0.834</v>
+        <v>3.305</v>
       </c>
       <c r="E12">
-        <v>0.877</v>
+        <v>3.533</v>
       </c>
     </row>
     <row r="13">
@@ -574,16 +574,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.8755458515283843</v>
+        <v>3.478384279475982</v>
       </c>
       <c r="C13">
-        <v>0.876</v>
+        <v>3.478</v>
       </c>
       <c r="D13">
-        <v>0.852</v>
+        <v>3.354</v>
       </c>
       <c r="E13">
-        <v>0.899</v>
+        <v>3.602</v>
       </c>
     </row>
     <row r="14">
@@ -591,16 +591,16 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.8083842794759826</v>
+        <v>3.217205240174672</v>
       </c>
       <c r="C14">
-        <v>0.8080000000000001</v>
+        <v>3.217</v>
       </c>
       <c r="D14">
-        <v>0.787</v>
+        <v>3.108</v>
       </c>
       <c r="E14">
-        <v>0.829</v>
+        <v>3.326</v>
       </c>
     </row>
     <row r="15">
@@ -608,16 +608,16 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>0.7965065502183406</v>
+        <v>3.146899563318777</v>
       </c>
       <c r="C15">
-        <v>0.797</v>
+        <v>3.147</v>
       </c>
       <c r="D15">
-        <v>0.775</v>
+        <v>3.034</v>
       </c>
       <c r="E15">
-        <v>0.8179999999999999</v>
+        <v>3.262</v>
       </c>
     </row>
     <row r="16">
@@ -625,16 +625,16 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>0.7527510917030568</v>
+        <v>2.972314410480349</v>
       </c>
       <c r="C16">
-        <v>0.753</v>
+        <v>2.972</v>
       </c>
       <c r="D16">
-        <v>0.732</v>
+        <v>2.861</v>
       </c>
       <c r="E16">
-        <v>0.773</v>
+        <v>3.081</v>
       </c>
     </row>
     <row r="17">
@@ -642,16 +642,16 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>0.72882096069869</v>
+        <v>2.887772925764192</v>
       </c>
       <c r="C17">
-        <v>0.729</v>
+        <v>2.888</v>
       </c>
       <c r="D17">
-        <v>0.708</v>
+        <v>2.778</v>
       </c>
       <c r="E17">
-        <v>0.75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -659,16 +659,16 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>0.6894323144104804</v>
+        <v>2.788427947598253</v>
       </c>
       <c r="C18">
-        <v>0.6889999999999999</v>
+        <v>2.788</v>
       </c>
       <c r="D18">
-        <v>0.669</v>
+        <v>2.68</v>
       </c>
       <c r="E18">
-        <v>0.709</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="19">
@@ -676,16 +676,16 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>0.6763755458515284</v>
+        <v>2.725152838427948</v>
       </c>
       <c r="C19">
-        <v>0.676</v>
+        <v>2.725</v>
       </c>
       <c r="D19">
-        <v>0.656</v>
+        <v>2.619</v>
       </c>
       <c r="E19">
-        <v>0.697</v>
+        <v>2.833</v>
       </c>
     </row>
     <row r="20">
@@ -693,16 +693,16 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.667117903930131</v>
+        <v>2.677423580786026</v>
       </c>
       <c r="C20">
-        <v>0.667</v>
+        <v>2.677</v>
       </c>
       <c r="D20">
-        <v>0.647</v>
+        <v>2.572</v>
       </c>
       <c r="E20">
-        <v>0.6870000000000001</v>
+        <v>2.779</v>
       </c>
     </row>
     <row r="21">
@@ -710,16 +710,16 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0.62</v>
+        <v>2.480829694323144</v>
       </c>
       <c r="C21">
-        <v>0.62</v>
+        <v>2.481</v>
       </c>
       <c r="D21">
-        <v>0.6</v>
+        <v>2.377</v>
       </c>
       <c r="E21">
-        <v>0.639</v>
+        <v>2.581</v>
       </c>
     </row>
     <row r="22">
@@ -727,16 +727,16 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>0.6348908296943231</v>
+        <v>2.539475982532751</v>
       </c>
       <c r="C22">
-        <v>0.635</v>
+        <v>2.539</v>
       </c>
       <c r="D22">
-        <v>0.615</v>
+        <v>2.433</v>
       </c>
       <c r="E22">
-        <v>0.654</v>
+        <v>2.641</v>
       </c>
     </row>
     <row r="23">
@@ -744,16 +744,16 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>0.5775545851528384</v>
+        <v>2.363580786026201</v>
       </c>
       <c r="C23">
-        <v>0.578</v>
+        <v>2.364</v>
       </c>
       <c r="D23">
-        <v>0.5590000000000001</v>
+        <v>2.264</v>
       </c>
       <c r="E23">
-        <v>0.596</v>
+        <v>2.464</v>
       </c>
     </row>
     <row r="24">
@@ -761,16 +761,16 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>0.5849344978165939</v>
+        <v>2.361703056768559</v>
       </c>
       <c r="C24">
-        <v>0.585</v>
+        <v>2.362</v>
       </c>
       <c r="D24">
-        <v>0.5659999999999999</v>
+        <v>2.267</v>
       </c>
       <c r="E24">
-        <v>0.605</v>
+        <v>2.462</v>
       </c>
     </row>
     <row r="25">
@@ -778,16 +778,16 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>0.5317903930131004</v>
+        <v>2.149956331877729</v>
       </c>
       <c r="C25">
-        <v>0.532</v>
+        <v>2.15</v>
       </c>
       <c r="D25">
-        <v>0.513</v>
+        <v>2.049</v>
       </c>
       <c r="E25">
-        <v>0.55</v>
+        <v>2.246</v>
       </c>
     </row>
   </sheetData>
@@ -832,16 +832,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2.351294036181078</v>
+        <v>6.239072102484204</v>
       </c>
       <c r="C2">
-        <v>2.351</v>
+        <v>6.239</v>
       </c>
       <c r="D2">
-        <v>2.32</v>
+        <v>6.175</v>
       </c>
       <c r="E2">
-        <v>2.383</v>
+        <v>6.305</v>
       </c>
     </row>
     <row r="3">
@@ -849,16 +849,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1.632086903834502</v>
+        <v>3.844758937072622</v>
       </c>
       <c r="C3">
-        <v>1.632</v>
+        <v>3.845</v>
       </c>
       <c r="D3">
-        <v>1.604</v>
+        <v>3.787</v>
       </c>
       <c r="E3">
-        <v>1.659</v>
+        <v>3.902</v>
       </c>
     </row>
     <row r="4">
@@ -866,16 +866,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1.485241928503419</v>
+        <v>3.3102224530425</v>
       </c>
       <c r="C4">
-        <v>1.485</v>
+        <v>3.31</v>
       </c>
       <c r="D4">
-        <v>1.459</v>
+        <v>3.255</v>
       </c>
       <c r="E4">
-        <v>1.512</v>
+        <v>3.365</v>
       </c>
     </row>
     <row r="5">
@@ -883,16 +883,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1.226910759110188</v>
+        <v>2.692330996278023</v>
       </c>
       <c r="C5">
-        <v>1.227</v>
+        <v>2.692</v>
       </c>
       <c r="D5">
-        <v>1.203</v>
+        <v>2.644</v>
       </c>
       <c r="E5">
-        <v>1.251</v>
+        <v>2.741</v>
       </c>
     </row>
     <row r="6">
@@ -900,16 +900,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1.119968839262529</v>
+        <v>2.4432182117199</v>
       </c>
       <c r="C6">
-        <v>1.12</v>
+        <v>2.443</v>
       </c>
       <c r="D6">
-        <v>1.096</v>
+        <v>2.386</v>
       </c>
       <c r="E6">
-        <v>1.144</v>
+        <v>2.499</v>
       </c>
     </row>
     <row r="7">
@@ -917,16 +917,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.9996537695836579</v>
+        <v>2.15714533021726</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>2.157</v>
       </c>
       <c r="D7">
-        <v>0.978</v>
+        <v>2.11</v>
       </c>
       <c r="E7">
-        <v>1.022</v>
+        <v>2.204</v>
       </c>
     </row>
     <row r="8">
@@ -934,16 +934,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.9562018523327275</v>
+        <v>2.046178481779624</v>
       </c>
       <c r="C8">
-        <v>0.956</v>
+        <v>2.046</v>
       </c>
       <c r="D8">
-        <v>0.9340000000000001</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>0.978</v>
+        <v>2.092</v>
       </c>
     </row>
     <row r="9">
@@ -951,16 +951,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.8657491560633601</v>
+        <v>1.860036354193716</v>
       </c>
       <c r="C9">
-        <v>0.866</v>
+        <v>1.86</v>
       </c>
       <c r="D9">
-        <v>0.844</v>
+        <v>1.815</v>
       </c>
       <c r="E9">
-        <v>0.887</v>
+        <v>1.904</v>
       </c>
     </row>
     <row r="10">
@@ -968,16 +968,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.8558383103955682</v>
+        <v>1.818834934649009</v>
       </c>
       <c r="C10">
-        <v>0.856</v>
+        <v>1.819</v>
       </c>
       <c r="D10">
-        <v>0.835</v>
+        <v>1.776</v>
       </c>
       <c r="E10">
-        <v>0.877</v>
+        <v>1.863</v>
       </c>
     </row>
     <row r="11">
@@ -985,16 +985,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.8204795291266338</v>
+        <v>1.754003289188955</v>
       </c>
       <c r="C11">
-        <v>0.82</v>
+        <v>1.754</v>
       </c>
       <c r="D11">
-        <v>0.799</v>
+        <v>1.711</v>
       </c>
       <c r="E11">
-        <v>0.841</v>
+        <v>1.796</v>
       </c>
     </row>
     <row r="12">
@@ -1002,16 +1002,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.7699298883406908</v>
+        <v>1.641262009867567</v>
       </c>
       <c r="C12">
-        <v>0.77</v>
+        <v>1.641</v>
       </c>
       <c r="D12">
-        <v>0.749</v>
+        <v>1.593</v>
       </c>
       <c r="E12">
-        <v>0.79</v>
+        <v>1.688</v>
       </c>
     </row>
     <row r="13">
@@ -1019,16 +1019,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.7911797801436856</v>
+        <v>1.679650307279495</v>
       </c>
       <c r="C13">
-        <v>0.791</v>
+        <v>1.68</v>
       </c>
       <c r="D13">
-        <v>0.77</v>
+        <v>1.633</v>
       </c>
       <c r="E13">
-        <v>0.8139999999999999</v>
+        <v>1.731</v>
       </c>
     </row>
     <row r="14">
@@ -1036,16 +1036,16 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.7280360079632996</v>
+        <v>1.519908248939669</v>
       </c>
       <c r="C14">
-        <v>0.728</v>
+        <v>1.52</v>
       </c>
       <c r="D14">
-        <v>0.709</v>
+        <v>1.481</v>
       </c>
       <c r="E14">
-        <v>0.748</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="15">
@@ -1053,16 +1053,16 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>0.7175625378689517</v>
+        <v>1.513416428633255</v>
       </c>
       <c r="C15">
-        <v>0.718</v>
+        <v>1.513</v>
       </c>
       <c r="D15">
-        <v>0.697</v>
+        <v>1.473</v>
       </c>
       <c r="E15">
-        <v>0.737</v>
+        <v>1.553</v>
       </c>
     </row>
     <row r="16">
@@ -1070,16 +1070,16 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>0.6809919501428201</v>
+        <v>1.423050289967974</v>
       </c>
       <c r="C16">
-        <v>0.681</v>
+        <v>1.423</v>
       </c>
       <c r="D16">
-        <v>0.661</v>
+        <v>1.384</v>
       </c>
       <c r="E16">
-        <v>0.701</v>
+        <v>1.461</v>
       </c>
     </row>
     <row r="17">
@@ -1087,16 +1087,16 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>0.6538128624599671</v>
+        <v>1.389336103176664</v>
       </c>
       <c r="C17">
-        <v>0.654</v>
+        <v>1.389</v>
       </c>
       <c r="D17">
-        <v>0.635</v>
+        <v>1.352</v>
       </c>
       <c r="E17">
-        <v>0.673</v>
+        <v>1.428</v>
       </c>
     </row>
     <row r="18">
@@ -1104,16 +1104,16 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>0.6206613000952134</v>
+        <v>1.314723448454947</v>
       </c>
       <c r="C18">
-        <v>0.621</v>
+        <v>1.315</v>
       </c>
       <c r="D18">
-        <v>0.603</v>
+        <v>1.278</v>
       </c>
       <c r="E18">
-        <v>0.639</v>
+        <v>1.353</v>
       </c>
     </row>
     <row r="19">
@@ -1121,16 +1121,16 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>0.6067255258374448</v>
+        <v>1.299056522115468</v>
       </c>
       <c r="C19">
-        <v>0.607</v>
+        <v>1.299</v>
       </c>
       <c r="D19">
-        <v>0.589</v>
+        <v>1.263</v>
       </c>
       <c r="E19">
-        <v>0.624</v>
+        <v>1.336</v>
       </c>
     </row>
     <row r="20">
@@ -1138,16 +1138,16 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.6009694451657578</v>
+        <v>1.288756167229291</v>
       </c>
       <c r="C20">
-        <v>0.601</v>
+        <v>1.289</v>
       </c>
       <c r="D20">
-        <v>0.583</v>
+        <v>1.249</v>
       </c>
       <c r="E20">
-        <v>0.62</v>
+        <v>1.328</v>
       </c>
     </row>
     <row r="21">
@@ -1155,16 +1155,16 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0.5577339219250411</v>
+        <v>1.18648835800225</v>
       </c>
       <c r="C21">
-        <v>0.5580000000000001</v>
+        <v>1.186</v>
       </c>
       <c r="D21">
-        <v>0.54</v>
+        <v>1.151</v>
       </c>
       <c r="E21">
-        <v>0.576</v>
+        <v>1.224</v>
       </c>
     </row>
     <row r="22">
@@ -1172,16 +1172,16 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>0.5709339565480828</v>
+        <v>1.205574309703108</v>
       </c>
       <c r="C22">
-        <v>0.571</v>
+        <v>1.206</v>
       </c>
       <c r="D22">
-        <v>0.552</v>
+        <v>1.167</v>
       </c>
       <c r="E22">
-        <v>0.589</v>
+        <v>1.243</v>
       </c>
     </row>
     <row r="23">
@@ -1189,16 +1189,16 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>0.517441357223232</v>
+        <v>1.113823249372457</v>
       </c>
       <c r="C23">
-        <v>0.517</v>
+        <v>1.114</v>
       </c>
       <c r="D23">
-        <v>0.501</v>
+        <v>1.079</v>
       </c>
       <c r="E23">
-        <v>0.534</v>
+        <v>1.148</v>
       </c>
     </row>
     <row r="24">
@@ -1206,16 +1206,16 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>0.5291266337747771</v>
+        <v>1.112351770103003</v>
       </c>
       <c r="C24">
-        <v>0.529</v>
+        <v>1.112</v>
       </c>
       <c r="D24">
-        <v>0.511</v>
+        <v>1.075</v>
       </c>
       <c r="E24">
-        <v>0.547</v>
+        <v>1.149</v>
       </c>
     </row>
     <row r="25">
@@ -1223,16 +1223,16 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>0.4809573271011858</v>
+        <v>1.036873539340431</v>
       </c>
       <c r="C25">
-        <v>0.481</v>
+        <v>1.037</v>
       </c>
       <c r="D25">
-        <v>0.465</v>
+        <v>1.003</v>
       </c>
       <c r="E25">
-        <v>0.497</v>
+        <v>1.071</v>
       </c>
     </row>
   </sheetData>
